--- a/output/pdf_financials_xlsx/SSA.xlsx
+++ b/output/pdf_financials_xlsx/SSA.xlsx
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001539</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.031394</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.042676</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.036477</v>
       </c>
     </row>
     <row r="13">
@@ -1564,16 +1564,16 @@
         <v>0.387721</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.168848</v>
+        <v>0.167309</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.387159</v>
+        <v>0.355765</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.214427</v>
+        <v>0.171751</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.08695899999999999</v>
+        <v>0.050482</v>
       </c>
     </row>
     <row r="28">
@@ -1644,16 +1644,16 @@
         <v>0.387721</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.168848</v>
+        <v>0.167309</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.387159</v>
+        <v>0.355765</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.214427</v>
+        <v>0.171751</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.08695899999999999</v>
+        <v>0.050482</v>
       </c>
     </row>
     <row r="30">
@@ -1684,16 +1684,16 @@
         <v>22.90314920442892</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.22115735017973</v>
+        <v>10.12799449860952</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>18.64095367819861</v>
+        <v>17.12939357040474</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>12.94206619661013</v>
+        <v>10.36629161128957</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>5.185801855484066</v>
+        <v>3.010495167476014</v>
       </c>
     </row>
     <row r="31">
@@ -1790,25 +1790,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.012822</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.019923</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.047083</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.043849</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.122954</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.130829</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.877547</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.073067</v>
@@ -1870,25 +1870,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.012822</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.019923</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.047083</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.043849</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.122954</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.130829</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.877547</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.073067</v>
@@ -2350,25 +2350,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.032155</v>
+        <v>0.019333</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.045524</v>
+        <v>0.025601</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.072419</v>
+        <v>0.025336</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.066716</v>
+        <v>0.022867</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.302691</v>
+        <v>0.179737</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.310566</v>
+        <v>0.179737</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.212582</v>
+        <v>0.335035</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.190287</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">

--- a/output/pdf_financials_xlsx/SSA.xlsx
+++ b/output/pdf_financials_xlsx/SSA.xlsx
@@ -3132,37 +3132,37 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.055773</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.052305</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.038476</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.065928</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.100274</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.047258</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.065244</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.052345</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.056882</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.038397</v>
       </c>
     </row>
     <row r="68">
@@ -3172,37 +3172,37 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.055773</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.052305</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.038476</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.065928</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.100274</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.047258</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.065244</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.052345</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.056882</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.038397</v>
       </c>
     </row>
     <row r="69">
@@ -3452,37 +3452,37 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.013894</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.011006</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.037915</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.982089</v>
+        <v>0.916161</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.169902</v>
+        <v>0.069628</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.149264</v>
+        <v>0.102006</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.358468</v>
+        <v>0.293224</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.126727</v>
+        <v>0.074382</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.212026</v>
+        <v>0.155144</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.275787</v>
+        <v>0.23739</v>
       </c>
     </row>
     <row r="76">
@@ -4910,13 +4910,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -5079,10 +5079,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.00346</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.055545</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -5892,13 +5892,13 @@
         <v>0.081815</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.188897</v>
+        <v>0.185897</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>0.493143</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.58431</v>
+        <v>0.57031</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>0.434738</v>
@@ -17198,7 +17198,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -18493,7 +18497,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -19339,7 +19347,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
